--- a/genex-parent/data/parent_2_4/activity_family_taxonomy_v1.xlsx
+++ b/genex-parent/data/parent_2_4/activity_family_taxonomy_v1.xlsx
@@ -463,7 +463,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -474,7 +473,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,7 +485,6 @@
           <t>learning_and_thinking</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>OT;SLP</t>
@@ -498,7 +495,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,7 +507,6 @@
           <t>fine_motor</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>OT</t>
@@ -522,7 +517,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,7 +544,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -578,7 +571,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -606,7 +598,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,7 +610,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -630,7 +620,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -643,7 +632,6 @@
           <t>fine_motor</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>OT</t>
@@ -654,7 +642,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -667,7 +654,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -678,7 +664,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -706,7 +691,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -719,14 +703,11 @@
           <t>social_and_emotional</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -739,7 +720,6 @@
           <t>gross_motor</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
@@ -750,7 +730,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -763,7 +742,6 @@
           <t>learning_and_thinking</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -774,7 +752,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -802,7 +779,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -830,7 +806,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -858,7 +833,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -886,7 +860,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -914,7 +887,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -927,7 +899,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -938,7 +909,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -966,7 +936,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -979,7 +948,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -990,7 +958,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1003,7 +970,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -1014,7 +980,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1027,14 +992,11 @@
           <t>social_and_emotional</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1062,7 +1024,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1090,7 +1051,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1118,7 +1078,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1146,7 +1105,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1159,7 +1117,6 @@
           <t>gross_motor</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>PT</t>
@@ -1170,7 +1127,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1198,7 +1154,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1211,7 +1166,6 @@
           <t>gross_motor</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>PT</t>
@@ -1222,7 +1176,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1235,14 +1188,11 @@
           <t>social_and_emotional</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1270,7 +1220,6 @@
           <t>ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1283,7 +1232,6 @@
           <t>learning_and_thinking</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>OT</t>
@@ -1294,7 +1242,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1322,7 +1269,6 @@
           <t>ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1335,7 +1281,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -1346,7 +1291,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1359,7 +1303,6 @@
           <t>learning_and_thinking</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>OT</t>
@@ -1370,7 +1313,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1398,7 +1340,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1426,7 +1367,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1439,7 +1379,6 @@
           <t>fine_motor</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>OT</t>
@@ -1450,7 +1389,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1463,7 +1401,6 @@
           <t>gross_motor</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>PT</t>
@@ -1474,7 +1411,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1502,7 +1438,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1530,7 +1465,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1543,7 +1477,6 @@
           <t>learning_and_thinking</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>OT</t>
@@ -1554,7 +1487,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1567,7 +1499,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -1578,7 +1509,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1606,7 +1536,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1634,7 +1563,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1647,7 +1575,6 @@
           <t>gross_motor</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>PT</t>
@@ -1658,7 +1585,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1671,7 +1597,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -1682,7 +1607,6 @@
           <t>ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1710,7 +1634,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1738,7 +1661,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1766,7 +1688,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1779,7 +1700,6 @@
           <t>gross_motor</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>PT</t>
@@ -1790,7 +1710,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1818,7 +1737,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1831,7 +1749,6 @@
           <t>talking_and_communicating</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>SLP</t>
@@ -1842,7 +1759,6 @@
           <t>Early Intervention Specialist;ECSE / Special Education Teacher</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1855,7 +1771,6 @@
           <t>learning_and_thinking</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>OT</t>
@@ -1866,7 +1781,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1879,7 +1793,6 @@
           <t>gross_motor</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>PT</t>
@@ -1890,7 +1803,6 @@
           <t>Early Intervention Specialist</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1903,7 +1815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,6 +1839,162 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>helper_role_chores</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>conversation_exchange</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>conversation_turn_taking</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>early_vocalization_sound_play</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>early_vocalizations</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>expressive_two_word_phrase</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>two_word_phrases</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>object_function_questions</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>function_question_answering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>receptive_direction</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>receptive_directions_one_step</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>story_narration</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>narration_storytelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>expressive_three_words</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>expressive_first_words</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>four_word_sentences</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sentence_building</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gesture_request_pickup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gesture_communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gesture_requesting</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gesture_communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gesture_variety</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gesture_communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gesture_waving</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>gesture_communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>receptive_direction_with_gesture</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>receptive_directions_one_step</t>
         </is>
       </c>
     </row>

--- a/genex-parent/data/parent_2_4/activity_family_taxonomy_v1.xlsx
+++ b/genex-parent/data/parent_2_4/activity_family_taxonomy_v1.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_families" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity_family_aliases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="canonical_domains" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="professional_roles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadata" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="activity_families" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="activity_family_aliases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="canonical_domains" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="professional_roles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="metadata" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unresolved_family_register" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2247,4 +2248,222 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>family_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>resolution_status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>review_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pronouns</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>deferred_post_pilot</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Personal pronoun production (I/me/we). No existing family is right: expressive_vocabulary_growth measures vocabulary QUANTITY, not a grammatical class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>receptive_object_identification</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>deferred_post_pilot</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Receptive object identification. Deferred: needs a reviewed definition before it exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rhyming</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>deferred_post_pilot</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Rhyme awareness and production. Deferred: needs a reviewed definition before it exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sound_response_orientation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>deferred_post_pilot</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Responsive vocalisation to speech. Closest existing family is early_vocalizations, which already binds the 6m vocal turn-taking rung; an alias was deliberately NOT created in this slice because the 4m rung is irrelevant to the 3-5y pilot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>speech_intelligibility</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>deferred_post_pilot</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Speech intelligibility. Deferred: needs a reviewed definition before it exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>story_comprehension</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>deferred_post_pilot</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RECEPTIVE narrative. Must never alias onto narration_storytelling, which is expressive; that merge would broaden a family beyond what it was reviewed for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>wh_question_asking</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>deferred_post_pilot</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The child ASKS who/what/where/why. Must never alias onto function_question_answering, where the child ANSWERS: the merge would silently invert who produces the question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>daily_recall_narrative</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ambiguous_unresolved</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Could be claimed by narration_storytelling or by a conversation family. Aliasing either would be a guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>expressive_name_response</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ambiguous_unresolved</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Simultaneously question-answering, personal-information vocabulary and a social-response routine. function_question_answering is scoped to OBJECT FUNCTION at 48m, so claiming it would mis-scope that family and collide with the 48m band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>receptive_stop_no</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ambiguous_unresolved</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Could be claimed by a receptive-directions family or a social-regulation family. Aliasing either would be a guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>song_story_words</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ambiguous_unresolved</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Could be claimed by narration_storytelling, book_object_naming or an imitation family. Aliasing any would be a guess.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>